--- a/kahoot/week02.xlsx
+++ b/kahoot/week02.xlsx
@@ -14,7 +14,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kahoot! quiz — question import</t>
+          <t xml:space="preserve">Kahoot! quiz - question import</t>
         </is>
       </c>
     </row>
@@ -105,15 +105,11 @@
           <t xml:space="preserve">G is satisfiable</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
+      <c r="F9">
+        <v>30</v>
+      </c>
+      <c r="G9">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -142,15 +138,11 @@
           <t xml:space="preserve">only if A is a tautology</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
+      <c r="F10">
+        <v>30</v>
+      </c>
+      <c r="G10">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -179,15 +171,11 @@
           <t xml:space="preserve">A -&gt; not A</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
+      <c r="F11">
+        <v>30</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -216,15 +204,11 @@
           <t xml:space="preserve">satisfiable only if C=1</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
+      <c r="F12">
+        <v>30</v>
+      </c>
+      <c r="G12">
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -253,15 +237,11 @@
           <t xml:space="preserve">Is B true?</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">60</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
+      <c r="F13">
+        <v>60</v>
+      </c>
+      <c r="G13">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -290,15 +270,11 @@
           <t xml:space="preserve">only for prime x</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
+      <c r="F14">
+        <v>30</v>
+      </c>
+      <c r="G14">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -327,15 +303,11 @@
           <t xml:space="preserve">there is x with P(x)</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
+      <c r="F15">
+        <v>30</v>
+      </c>
+      <c r="G15">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -364,15 +336,11 @@
           <t xml:space="preserve">not a statement</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
+      <c r="F16">
+        <v>30</v>
+      </c>
+      <c r="G16">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/kahoot/week02.xlsx
+++ b/kahoot/week02.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G22"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -82,265 +82,423 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">F |= G means:</t>
+          <t xml:space="preserve">Which of the following is a mathematical statement?</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">F -&gt; G is a formula</t>
+          <t xml:space="preserve">71 is a prime number</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">every assignment satisfying F satisfies G</t>
+          <t xml:space="preserve">It might rain today</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">F and G have the same symbols</t>
+          <t xml:space="preserve">A ∧ ¬B</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">G is satisfiable</t>
+          <t xml:space="preserve">x + 1 = 2</t>
         </is>
       </c>
       <c r="F9">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Does A -&gt; B |= not A -&gt; not B hold?</t>
+          <t xml:space="preserve">F ⊨ G means:</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">every truth assignment that makes F true makes G true</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">no, take A=0 and B=1</t>
+          <t xml:space="preserve">F → G is true for at least one truth assignment</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">no, take A=1 and B=1</t>
+          <t xml:space="preserve">G is a tautology</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">only if A is a tautology</t>
+          <t xml:space="preserve">F is satisfiable</t>
         </is>
       </c>
       <c r="F10">
         <v>30</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Which is always true?</t>
+          <t xml:space="preserve">True or false: B ∧ (A → B) ⊨ A</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">(A-&gt;B) or (B-&gt;A)</t>
+          <t xml:space="preserve">True</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">(A-&gt;B) and (B-&gt;A)</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A and not A</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A -&gt; not A</t>
+          <t xml:space="preserve">False</t>
         </is>
       </c>
       <c r="F11">
         <v>30</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">((A-&gt;B) and (B-&gt;C)) and not(A-&gt;C) is:</t>
+          <t xml:space="preserve">Which formula is a tautology?</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">a tautology</t>
+          <t xml:space="preserve">A → (A ∨ B)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">satisfiable but not valid</t>
+          <t xml:space="preserve">A → (A ∧ B)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">unsatisfiable</t>
+          <t xml:space="preserve">(A ∨ B) → A</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">satisfiable only if C=1</t>
+          <t xml:space="preserve">A ∧ ¬A</t>
         </is>
       </c>
       <c r="F12">
         <v>30</v>
       </c>
       <c r="G12">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Knights tell the truth, knaves lie. Which question reveals whether the left road is right?</t>
+          <t xml:space="preserve">Which formula is unsatisfiable?</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Is A true?</t>
+          <t xml:space="preserve">(A → B) ∧ A ∧ ¬B</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Is A &lt;-&gt; B true?</t>
+          <t xml:space="preserve">(A → B) ∧ ¬A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Is A and B true?</t>
+          <t xml:space="preserve">A ↔ ¬B</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Is B true?</t>
+          <t xml:space="preserve">A → ¬A</t>
         </is>
       </c>
       <c r="F13">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="G13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">In Z, is 'for all x there is y with xy=1' true?</t>
+          <t xml:space="preserve">For formulas F and G, F → G is a tautology if and only if:</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">F ⊨ G</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">no, x=0 has no inverse</t>
+          <t xml:space="preserve">G ⊨ F</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">only for positive x</t>
+          <t xml:space="preserve">F is a tautology</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">only for prime x</t>
+          <t xml:space="preserve">G is satisfiable</t>
         </is>
       </c>
       <c r="F14">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">The negation of 'for all x, P(x)' is:</t>
+          <t xml:space="preserve">A ∨ ¬A is a tautology. Why is (B → C) ∨ ¬(B → C) one too?</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">for all x, not P(x)</t>
+          <t xml:space="preserve">lifting: replace A by the formula B → C</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">there is x with not P(x)</t>
+          <t xml:space="preserve">de Morgan's rules</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">not there is x with P(x)</t>
+          <t xml:space="preserve">double negation</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">there is x with P(x)</t>
+          <t xml:space="preserve">it is not a tautology</t>
         </is>
       </c>
       <c r="F15">
         <v>30</v>
       </c>
       <c r="G15">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Every even number &gt; 2 is a sum of two primes. This statement is:</t>
+          <t xml:space="preserve">True or false: ∀x P(x) ∧ ∀x Q(x) ≡ ∀x (P(x) ∧ Q(x))</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">True</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">true and proved</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">a statement whose truth value is unknown</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">not a statement</t>
+          <t xml:space="preserve">False</t>
         </is>
       </c>
       <c r="F16">
         <v>30</v>
       </c>
       <c r="G16">
-        <v>3</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">True or false: ∃x (P(x) ∧ Q(x)) ≡ ∃x P(x) ∧ ∃x Q(x)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">True</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">False</t>
+        </is>
+      </c>
+      <c r="F17">
+        <v>30</v>
+      </c>
+      <c r="G17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">True or false: ∃y ∀x P(x, y) ⊨ ∀x ∃y P(x, y)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">True</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">False</t>
+        </is>
+      </c>
+      <c r="F18">
+        <v>30</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Which formula is equivalent to ¬∀x P(x)?</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">∃x ¬P(x)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">∀x ¬P(x)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">¬∃x P(x)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">∃x P(x)</t>
+        </is>
+      </c>
+      <c r="F19">
+        <v>20</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The formula ∃x P(x), with the universe and P not fixed, is:</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a formula, not a mathematical statement</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a true statement</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a false statement</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a tautology</t>
+        </is>
+      </c>
+      <c r="F20">
+        <v>30</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">An indirect proof of S ⟹ T:</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">assumes T is false and proves S is false</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">assumes S is false and proves T is false</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">assumes T and proves S</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">assumes S and proves T</t>
+        </is>
+      </c>
+      <c r="F21">
+        <v>30</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">To prove S by modus ponens, you find a statement R, prove R, and then prove:</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R ⟹ S</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S ⟹ R</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">¬R ⟹ ¬S</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R ⟹ ¬S</t>
+        </is>
+      </c>
+      <c r="F22">
+        <v>30</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
